--- a/Result/profitability/3095.xlsx
+++ b/Result/profitability/3095.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08374999999999999</v>
+        <v>0.15375</v>
       </c>
       <c r="N2" t="n">
-        <v>18.44</v>
+        <v>18.3925</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04499999999999998</v>
+        <v>0.0775</v>
       </c>
       <c r="N3" t="n">
-        <v>16.925</v>
+        <v>17.7125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04250000000000001</v>
+        <v>0.28625</v>
       </c>
       <c r="N4" t="n">
-        <v>16.92</v>
+        <v>17.70625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.009999999999999981</v>
+        <v>0.3275</v>
       </c>
       <c r="N5" t="n">
-        <v>16.00125</v>
+        <v>16.36375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07625000000000001</v>
+        <v>0.21625</v>
       </c>
       <c r="N6" t="n">
-        <v>14.6175</v>
+        <v>15.13625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01625000000000001</v>
+        <v>0.03500000000000002</v>
       </c>
       <c r="N7" t="n">
-        <v>13.87</v>
+        <v>13.8825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3525</v>
+        <v>-0.32375</v>
       </c>
       <c r="N8" t="n">
-        <v>13.5275</v>
+        <v>13.26375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3095</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>205</v>
+      </c>
+      <c r="D75" t="n">
+        <v>162</v>
+      </c>
+      <c r="E75" t="n">
+        <v>43</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="G75" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.14875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.77375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.109999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09157986111111105</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.569767441860465</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1608430393788129</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
